--- a/Models/Свиньи/results/Свиньи - Результаты прогнозов Prophet средние.xlsx
+++ b/Models/Свиньи/results/Свиньи - Результаты прогнозов Prophet средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>186.54</v>
+        <v>190.3</v>
       </c>
       <c r="C2" t="n">
-        <v>151.53</v>
+        <v>147.15</v>
       </c>
       <c r="D2" t="n">
-        <v>27.95</v>
+        <v>31.66</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52.4</v>
+        <v>51.28</v>
       </c>
       <c r="C3" t="n">
-        <v>43.36</v>
+        <v>42.91</v>
       </c>
       <c r="D3" t="n">
-        <v>61.17</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>149.96</v>
+        <v>98.59</v>
       </c>
       <c r="C4" t="n">
-        <v>132.93</v>
+        <v>90.38</v>
       </c>
       <c r="D4" t="n">
-        <v>191.75</v>
+        <v>308.04</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.4</v>
+        <v>0.22</v>
       </c>
       <c r="C5" t="n">
-        <v>0.83</v>
+        <v>0.13</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123.56</v>
+        <v>75.66</v>
       </c>
       <c r="C6" t="n">
-        <v>117.51</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>28.19</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="7">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C8" t="n">
         <v>0.02</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.01</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
@@ -563,13 +563,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.41</v>
+        <v>4.07</v>
       </c>
       <c r="C9" t="n">
-        <v>2.03</v>
+        <v>3.21</v>
       </c>
       <c r="D9" t="n">
-        <v>42.68</v>
+        <v>58.29</v>
       </c>
     </row>
     <row r="10">
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.44</v>
+        <v>15.72</v>
       </c>
       <c r="C10" t="n">
-        <v>11.27</v>
+        <v>13.11</v>
       </c>
       <c r="D10" t="n">
-        <v>32.11</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="11">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28.55</v>
+        <v>27.04</v>
       </c>
       <c r="C11" t="n">
-        <v>25.26</v>
+        <v>24.13</v>
       </c>
       <c r="D11" t="n">
-        <v>14.54</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="12">
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75.37</v>
+        <v>170.84</v>
       </c>
       <c r="C12" t="n">
-        <v>61.86</v>
+        <v>152.81</v>
       </c>
       <c r="D12" t="n">
-        <v>7.92</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="13">
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61.48</v>
+        <v>124.58</v>
       </c>
       <c r="C13" t="n">
-        <v>57.6</v>
+        <v>109.19</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="14">
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.46</v>
+        <v>12.52</v>
       </c>
       <c r="C14" t="n">
-        <v>8.23</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>128.32</v>
+        <v>62.14</v>
       </c>
     </row>
     <row r="15">
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>98.78</v>
+        <v>132.33</v>
       </c>
       <c r="C16" t="n">
-        <v>77.38</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>122.67</v>
+        <v>75.97</v>
       </c>
     </row>
     <row r="17">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>373.88</v>
+        <v>712.77</v>
       </c>
       <c r="C17" t="n">
-        <v>293.38</v>
+        <v>503.12</v>
       </c>
       <c r="D17" t="n">
-        <v>113.62</v>
+        <v>226.78</v>
       </c>
     </row>
     <row r="18">
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.02</v>
+        <v>613.4</v>
       </c>
       <c r="C18" t="n">
-        <v>0.82</v>
+        <v>354.66</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>189.61</v>
+        <v>365.37</v>
       </c>
       <c r="C19" t="n">
-        <v>149.43</v>
+        <v>319.57</v>
       </c>
       <c r="D19" t="n">
-        <v>9.15</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="20">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1156.58</v>
+        <v>783.34</v>
       </c>
       <c r="C20" t="n">
-        <v>976.14</v>
+        <v>667.6799999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>62.26</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="21">
@@ -751,12 +751,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="C21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>1.48</v>
+      </c>
+      <c r="D21" t="n">
+        <v>61.93</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
